--- a/property_management_forms/023_move_in_cost_payment_agreement_form--property_management_forms.xlsx
+++ b/property_management_forms/023_move_in_cost_payment_agreement_form--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2044,34 +2044,34 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>other_move_in_costs_option_1_choices</t>
+          <t>other_move_in_costs_option_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Parking</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>other_move_in_costs_option_1_choices</t>
+          <t>other_move_in_costs_option_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>storage</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Storage</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>parking</t>
+          <t>electricity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Parking</t>
+          <t>Electricity</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>electricity</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Gas</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>internet</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Internet</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Cable</t>
         </is>
       </c>
     </row>
@@ -2168,80 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>internet</t>
+          <t>security</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Internet</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>other_move_in_costs_option_2_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>cable</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Cable</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>other_move_in_costs_option_2_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>security</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
           <t>Security</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>other_move_in_costs_option_2_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>electricity</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>other_move_in_costs_option_2_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>water</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Water</t>
         </is>
       </c>
     </row>
